--- a/output/full_scan/batch_seq1_2026-10-12.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-12.xlsx
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>254.0163767320522</v>
+        <v>254.0163767320521</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>14.55</v>

--- a/output/full_scan/batch_seq1_2026-10-12.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-12.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1124</v>
+        <v>1404</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>16.05</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>68.33826630078501</v>
+        <v>68.33826620208777</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>43.47119058493366</v>
+        <v>43.47119057521634</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>5.432656587296376</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0388492314870062</v>
+        <v>0.0388492314990248</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1513</v>
+        <v>1563</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>939.8127062146392</v>
+        <v>1267.123943441211</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>169</v>
+        <v>87.2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>57.61927714029257</v>
+        <v>75.60923786476349</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9.349510608926661</v>
+        <v>41.76653473522637</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.618651590149156</v>
+        <v>3.797181059220249</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1960144782003979</v>
+        <v>0.53023733868263</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1530</v>
+        <v>1513</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>939</v>
+        <v>1129.81270621464</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.8</v>
+        <v>169</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.209197700548</v>
+        <v>57.61927714029257</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>24.63152109005442</v>
+        <v>9.349510655460872</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10.0902952856969</v>
+        <v>2.618651590149156</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1545659588260513</v>
+        <v>0.196014478080197</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1563</v>
+        <v>1101</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>872.1239434412112</v>
+        <v>1120.134850960792</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>87.2</v>
+        <v>27</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>75.60923783202145</v>
+        <v>67.66222986045608</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>41.76653453834152</v>
+        <v>41.07452652089489</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.797181059220249</v>
+        <v>3.092493277791588</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.5302373390327699</v>
+        <v>0.1368313299365642</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1101</v>
+        <v>1530</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>860.1348509607921</v>
+        <v>1109</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>27</v>
+        <v>28.8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>67.66222973746576</v>
+        <v>64.20919766020231</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>41.0745264606837</v>
+        <v>24.6315211337796</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.092493277791588</v>
+        <v>10.0902952856969</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1368313300807663</v>
+        <v>0.1545659587539459</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1519</v>
+        <v>1416</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>778.6171729173636</v>
+        <v>1038.585902364242</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>724</v>
+        <v>12.65</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.06559996457077</v>
+        <v>77.95159197841159</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>13.5070046474716</v>
+        <v>23.7636707750988</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.174414986188183</v>
+        <v>6.096398390980038</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.577779314335945</v>
+        <v>0.1010305864522107</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1514</v>
+        <v>1102</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>774.0309297432459</v>
+        <v>1038.494109952942</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>105</v>
+        <v>36.65</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.91103885118318</v>
+        <v>66.31528277594418</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>13.77344331748985</v>
+        <v>24.02022459614333</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.89271395351072</v>
+        <v>0.8017066944174551</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3138962395411276</v>
+        <v>0.0569109466631473</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1454</v>
+        <v>1503</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>774</v>
+        <v>1009.416034360292</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13.4</v>
+        <v>204</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>70.84291987583508</v>
+        <v>57.13329537949775</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>19.89170944405793</v>
+        <v>9.175644598116254</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7.56886967634327</v>
+        <v>3.141496810747636</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0663443186118987</v>
+        <v>0.6676308994401905</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1569</v>
+        <v>1305</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>761.8045462741542</v>
+        <v>978.6607300449864</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>73.7</v>
+        <v>13.15</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>77.8274886145245</v>
+        <v>66.24241298702185</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>64.00124138978438</v>
+        <v>23.72549595143088</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.219306859212607</v>
+        <v>1.466073004498625</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.8512824496493439</v>
+        <v>0.1070528665392396</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1416</v>
+        <v>1516</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>758.5859023642423</v>
+        <v>957.4948285994496</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12.65</v>
+        <v>15.4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>77.95159197841159</v>
+        <v>60.14272084152397</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>23.7636707750988</v>
+        <v>12.66299839574378</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.096398390980038</v>
+        <v>1.552855108943231</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1010305864642289</v>
+        <v>0.1948955341346228</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1314</v>
+        <v>1454</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>757.4525950834003</v>
+        <v>944</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9.039999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.20931324957179</v>
+        <v>70.84291985240017</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>41.3222048310944</v>
+        <v>19.89170953128536</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5018751397187682</v>
+        <v>7.56886967634327</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0013887477604137</v>
+        <v>0.0663443185998817</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1102</v>
+        <v>1569</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>738.4941099529423</v>
+        <v>931.8045462741542</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>36.65</v>
+        <v>73.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>66.31528255891874</v>
+        <v>77.82748846833564</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>24.02022453695486</v>
+        <v>64.00124146670879</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8017066944174551</v>
+        <v>1.219306859212607</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0569109468674363</v>
+        <v>0.8512824502502001</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>737.4948285994496</v>
+        <v>918.6171729173628</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15.4</v>
+        <v>724</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>60.14272083476504</v>
+        <v>56.06559995952443</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>12.66299828981291</v>
+        <v>13.50700464582671</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.552855108943231</v>
+        <v>4.174414986188183</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1948955341466394</v>
+        <v>1.57777931457635</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1503</v>
+        <v>1514</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>704.4160343602925</v>
+        <v>889.0309297432716</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.13329552100769</v>
+        <v>57.91103879009416</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>9.175644614722382</v>
+        <v>13.77344328414982</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.141496810747636</v>
+        <v>3.89271395351072</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.6676308990796853</v>
+        <v>0.3138962390604529</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1560</v>
+        <v>1434</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>687.1952810626448</v>
+        <v>875.1690821734533</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1000</v>
+        <v>19.45</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>69.55700751910115</v>
+        <v>70.8906802196046</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>50.42348829007576</v>
+        <v>29.88294419275818</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3403296129420832</v>
+        <v>2.116908217345326</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.920214308677004</v>
+        <v>0.1656691103514605</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1558</v>
+        <v>1301</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>680.2246722486001</v>
+        <v>875.060569524854</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>111.5</v>
+        <v>80.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.25872616416879</v>
+        <v>78.24352724763314</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>35.51109565502211</v>
+        <v>32.92723494876014</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9331608860201916</v>
+        <v>3.722546944058542</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.6895931208839015</v>
+        <v>1.525478348479716</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1456</v>
+        <v>1314</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>679.8983579535929</v>
+        <v>867.4525950834003</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>15.25</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>61.70803256736635</v>
+        <v>60.20931318625959</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.12602489677939</v>
+        <v>41.32220481808083</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6690980152046397</v>
+        <v>0.5018751397187682</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0544977381289132</v>
+        <v>0.0013887477532024</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>677.1986036370051</v>
+        <v>866.033913092809</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>21.6</v>
+        <v>32.95</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>57.41409275494986</v>
+        <v>61.46301486207533</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>16.94727295459083</v>
+        <v>8.8980601327758</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.119933111850794</v>
+        <v>0.915319618032534</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0029159611840332</v>
+        <v>0.030670506081809</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1313</v>
+        <v>1440</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>675.3800526659446</v>
+        <v>830.3607400749166</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>12.8</v>
+        <v>14.15</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.87295552989823</v>
+        <v>60.64649987595429</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>33.40456185267027</v>
+        <v>18.62064080038635</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.894758335273482</v>
+        <v>1.13607400749166</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0483640926417219</v>
+        <v>0.0936766122318201</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1305</v>
+        <v>1325</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>653.6607300449863</v>
+        <v>824</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13.15</v>
+        <v>31</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>66.24241302924341</v>
+        <v>81.90930177771622</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.72549599236211</v>
+        <v>31.23686193814262</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.466073004498625</v>
+        <v>12.60658867221844</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1070528665752892</v>
+        <v>0.5685882695375373</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1321</v>
+        <v>1477</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>641.0339130928086</v>
+        <v>805.4349033610313</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>32.95</v>
+        <v>205.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>61.46301486207533</v>
+        <v>63.28889560138155</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8.898060144026896</v>
+        <v>27.61837091396721</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.915319618032534</v>
+        <v>1.131298190016281</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.030670506105845</v>
+        <v>2.184742945852531</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1325</v>
+        <v>1560</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>624</v>
+        <v>797.1952810626451</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>31</v>
+        <v>1000</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>81.9093017714051</v>
+        <v>69.55700748589385</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.23686184810217</v>
+        <v>50.42348822218228</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12.60658867221844</v>
+        <v>0.3403296129420832</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5685882695255193</v>
+        <v>2.920214310359412</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1304</v>
+        <v>1409</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>611.1817443188668</v>
+        <v>790.558430316641</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13.1</v>
+        <v>26.1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>60.8528778366737</v>
+        <v>61.49711445002194</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>32.92651135868307</v>
+        <v>21.5871556959862</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.911470339786087</v>
+        <v>0.9796602129655244</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.076783999480738</v>
+        <v>0.1831601428614155</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1455</v>
+        <v>1216</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>596.7447318982158</v>
+        <v>789.6043301432239</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>10.2</v>
+        <v>76</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.52999511834488</v>
+        <v>56.61200233321239</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>34.25404978656071</v>
+        <v>14.42175005568601</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.627379932602835</v>
+        <v>1.036796978896781</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0536200718571512</v>
+        <v>0.2254051932947748</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1434</v>
+        <v>1323</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>595.1690821734533</v>
+        <v>787.1986036370051</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>19.45</v>
+        <v>21.6</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>70.8906802196046</v>
+        <v>57.41409264413637</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>29.88294424356949</v>
+        <v>16.94727295459083</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.116908217345326</v>
+        <v>1.119933111850794</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1656691103995307</v>
+        <v>0.0029159611960511</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1524</v>
+        <v>1319</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>585.6523575475576</v>
+        <v>785.4714740355768</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>27</v>
+        <v>81.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>61.7817059174329</v>
+        <v>60.94579767631272</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>30.30115132139358</v>
+        <v>16.90980913820515</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.493892721824277</v>
+        <v>1.142072193262662</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1393870234548639</v>
+        <v>0.2715935425895187</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1301</v>
+        <v>1313</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>580.0605695248543</v>
+        <v>785.3800526659444</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>80.7</v>
+        <v>12.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>78.24352724229189</v>
+        <v>64.8729553649322</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>32.92723486194615</v>
+        <v>33.40456186818552</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.722546944058542</v>
+        <v>1.894758335273482</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.525478348768128</v>
+        <v>0.0483640926176861</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1326</v>
+        <v>1504</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>560.141182337994</v>
+        <v>734.6914777526198</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>76.8</v>
+        <v>71.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>66.8061588756308</v>
+        <v>56.25975810649228</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>33.25308031627131</v>
+        <v>17.46549431301262</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.346168277548853</v>
+        <v>1.029227533167272</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.7960137053892644</v>
+        <v>0.3292819150684222</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1310</v>
+        <v>1326</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>556.3982831219724</v>
+        <v>730.141182337994</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>9.84</v>
+        <v>76.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>64.93806525715411</v>
+        <v>66.80615886825194</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>43.27986302581099</v>
+        <v>33.25308045725158</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.321286215008142</v>
+        <v>1.346168277548853</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1017897266339176</v>
+        <v>0.7960137052090088</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1441</v>
+        <v>1304</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>554.92885599436</v>
+        <v>726.1817443188685</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9.66</v>
+        <v>13.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.98103777610598</v>
+        <v>60.85287776209656</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26.87692858431702</v>
+        <v>32.92651136411568</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.86011783671324</v>
+        <v>1.911470339786087</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0511509444161831</v>
+        <v>0.0767839994326697</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1409</v>
+        <v>1476</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>550.5584303166405</v>
+        <v>725.9189849051465</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>26.1</v>
+        <v>312</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>61.49711471753029</v>
+        <v>65.88816260958495</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>21.58715568249024</v>
+        <v>37.85746213260709</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9796602129655244</v>
+        <v>1.419891702211936</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1831601428373805</v>
+        <v>5.346470228532813</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1315</v>
+        <v>1524</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>549.085528306614</v>
+        <v>725.6523575475539</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>73.3</v>
+        <v>27</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>87.0956246820755</v>
+        <v>61.78170579156226</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>50.44279038326829</v>
+        <v>30.30115125948148</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.157101001189087</v>
+        <v>1.493892721824277</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.4804432011606767</v>
+        <v>0.1393870233587262</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1308</v>
+        <v>1315</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>538.1082516202951</v>
+        <v>719.085528306614</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>14.65</v>
+        <v>73.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.81624142519035</v>
+        <v>87.0956246820755</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>36.13442477031942</v>
+        <v>50.44279025986084</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7968479853590047</v>
+        <v>1.157101001189087</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0276448980576579</v>
+        <v>0.4804432011366373</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1319</v>
+        <v>1455</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>535.4714740355768</v>
+        <v>711.7447318982159</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>81.7</v>
+        <v>10.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>60.94579760845832</v>
+        <v>55.52999512417426</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16.90980896709613</v>
+        <v>34.25404979990127</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.142072193262662</v>
+        <v>1.627379932602835</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2715935432384549</v>
+        <v>0.0536200718619591</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1476</v>
+        <v>1303</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>525.9189849051464</v>
+        <v>709.6531066934274</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>65.88816262795685</v>
+        <v>72.28123721642837</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>37.85746222041816</v>
+        <v>40.6556218331496</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.419891702211936</v>
+        <v>0.9866356752467116</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>5.34647023069592</v>
+        <v>5.894571910371329</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1477</v>
+        <v>1558</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>522.4407722699921</v>
+        <v>680.2246722486001</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>205.5</v>
+        <v>111.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>63.28889539332822</v>
+        <v>60.25872614533248</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.61837089533773</v>
+        <v>35.51109565502211</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8729665077478823</v>
+        <v>0.9331608860201916</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>2.184742947054253</v>
+        <v>-0.6895931211482971</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1342</v>
+        <v>1456</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>521.6199366656022</v>
+        <v>679.8983579535929</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>101.5</v>
+        <v>15.25</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.77757908288593</v>
+        <v>61.70803255328845</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>17.40803730274985</v>
+        <v>23.12602489677939</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.93351476417711</v>
+        <v>0.6690980152046397</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2338780825899212</v>
+        <v>0.0544977381289132</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1303</v>
+        <v>1310</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>509.6531066934274</v>
+        <v>671.3982831219724</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>303</v>
+        <v>9.84</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>72.28123718902434</v>
+        <v>64.93806505419275</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>40.65562170194947</v>
+        <v>43.27986320957931</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9866356752467116</v>
+        <v>1.321286215008142</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>5.894571911356728</v>
+        <v>0.1017897267084257</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1440</v>
+        <v>1402</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>505.3607400749166</v>
+        <v>648.7739497309054</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>14.15</v>
+        <v>28.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>60.64649987595429</v>
+        <v>56.51252460812304</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>18.62064078444824</v>
+        <v>12.51872986610502</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.13607400749166</v>
+        <v>1.167082925576753</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0936766122558539</v>
+        <v>0.06593460482240331</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1504</v>
+        <v>1104</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>504.6914777526197</v>
+        <v>607.5944764636504</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>71.7</v>
+        <v>27.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>56.25975803986667</v>
+        <v>57.60550827401007</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.46549431301262</v>
+        <v>12.77790736211117</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.029227533167272</v>
+        <v>1.27795185333914</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.3292819152366747</v>
+        <v>0.0331572627378289</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1103</v>
+        <v>1521</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>502.1307740616874</v>
+        <v>593.8802906092851</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>13.25</v>
+        <v>25.85</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.20632059726416</v>
+        <v>54.67282717998025</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>26.61750625638986</v>
+        <v>31.29590462237529</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.513077406168735</v>
+        <v>0.1996748805791123</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0137796068180508</v>
+        <v>0.0392146719201391</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1521</v>
+        <v>1229</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>483.8802906092847</v>
+        <v>577.198256857338</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>25.85</v>
+        <v>40.05</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.67282727593211</v>
+        <v>45.52496391534884</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>31.2959045324544</v>
+        <v>20.33034474586986</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.1996748805791123</v>
+        <v>0.7618320403960135</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0392146719441742</v>
+        <v>0.0153461709748139</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1229</v>
+        <v>1528</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>467.1982568573382</v>
+        <v>574.3009797991941</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>40.05</v>
+        <v>23.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45.52496408184805</v>
+        <v>48.65501555068023</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.33034473389619</v>
+        <v>36.00729560507295</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7618320403960135</v>
+        <v>0.1997823196362155</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0153461709507778</v>
+        <v>-0.3832710237596668</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1528</v>
+        <v>1441</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>464.3009797991942</v>
+        <v>554.92885599436</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>23.1</v>
+        <v>9.66</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.65501566073299</v>
+        <v>58.98103784032958</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>36.00729536266942</v>
+        <v>26.87692853654514</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.1997823196362155</v>
+        <v>1.86011783671324</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.3832710236755443</v>
+        <v>0.0511509443971125</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1418</v>
+        <v>1308</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>444.8731500542925</v>
+        <v>528.1082516202951</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>18.35</v>
+        <v>14.65</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>54.51443365517184</v>
+        <v>56.8162413926104</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>36.81030457728493</v>
+        <v>36.13442475135798</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3088194597535635</v>
+        <v>0.7968479853590047</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0601583910540675</v>
+        <v>0.0276448980095879</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1220</v>
+        <v>1342</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>438.8993823256216</v>
+        <v>521.6199366656022</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>10.95</v>
+        <v>101.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>56.55829447599088</v>
+        <v>51.7775789269439</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>21.07554648875478</v>
+        <v>17.40803730274985</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.099642602712516</v>
+        <v>1.93351476417711</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0284555683819281</v>
+        <v>0.2338780825658948</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1515</v>
+        <v>1103</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>428.9539520728241</v>
+        <v>502.1307740616874</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>29.1</v>
+        <v>13.25</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>44.67279171554273</v>
+        <v>55.20632059726416</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7.896105974021535</v>
+        <v>26.61750638476863</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.493842449877549</v>
+        <v>1.513077406168735</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0027923754440243</v>
+        <v>0.0137796067940163</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1402</v>
+        <v>1203</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>423.7739497309053</v>
+        <v>486.856886626764</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>28.7</v>
+        <v>43.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>56.51252458515937</v>
+        <v>49.46102422814432</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>12.51872986770624</v>
+        <v>10.03210660412672</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.167082925576753</v>
+        <v>0.1517528566099533</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0659346048464358</v>
+        <v>0.0396019612622814</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1236</v>
+        <v>1341</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>403.4649006676746</v>
+        <v>483.4423943245078</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>25.7</v>
+        <v>58.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.33099149021019</v>
+        <v>51.7646263430778</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.30742599813652</v>
+        <v>9.223265911961519</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5339450922550657</v>
+        <v>6.297784761719347</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0089230375713613</v>
+        <v>0.3057409360769048</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1210</v>
+        <v>1446</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>398.7098074262263</v>
+        <v>483.301275661966</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>51.3</v>
+        <v>13.45</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>39.1196293527881</v>
+        <v>46.79083564634488</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>26.94372853594444</v>
+        <v>15.83515275111071</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.04509588057432</v>
+        <v>0.7516506774851708</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0035072048833614</v>
+        <v>0.0093374395900357</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1445</v>
+        <v>1526</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>393.6468319297861</v>
+        <v>481.5606320712529</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>10.1</v>
+        <v>15.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45.80239318657009</v>
+        <v>50.62380713505777</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.68831634729692</v>
+        <v>17.90484467467044</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.671309860428899</v>
+        <v>1.118519962050936</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0384327356457416</v>
+        <v>0.1050200196565606</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1309</v>
+        <v>1419</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>388.8221355462224</v>
+        <v>474.5234532123402</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>14.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>55.63131080403725</v>
+        <v>48.92356559922494</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>34.81026814068846</v>
+        <v>11.56130391929785</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9390829491065809</v>
+        <v>0.6452856793427433</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0374020221076755</v>
+        <v>-0.0167566719954576</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1470</v>
+        <v>1531</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>385.0687972623247</v>
+        <v>470.2248658176511</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>24.1</v>
+        <v>11.85</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.45079635520776</v>
+        <v>50.60835549849367</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8.776718962544706</v>
+        <v>17.73031829046423</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2310998855305943</v>
+        <v>0.677402978779903</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0307734217726096</v>
+        <v>0.0558650888517329</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1104</v>
+        <v>1538</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>382.5944764636503</v>
+        <v>463.9546759462577</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>27.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>57.6055083465918</v>
+        <v>59.64563963578538</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.77790735949102</v>
+        <v>14.00432924692328</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.27795185333914</v>
+        <v>1.059549104037004</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0331572627378289</v>
+        <v>0.7258922245420879</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1439</v>
+        <v>1512</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>376.3785504971904</v>
+        <v>459.3010873250047</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>27.85</v>
+        <v>6.28</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.9551390431174</v>
+        <v>50.48943751732255</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.53079507923812</v>
+        <v>14.93214491694524</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.309262803046625</v>
+        <v>0.3509967936263382</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.5836781317836885</v>
+        <v>0.028356187828169</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1341</v>
+        <v>1220</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>373.4423943245078</v>
+        <v>458.8993823256216</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>58.7</v>
+        <v>10.95</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.76462634888596</v>
+        <v>56.55829416555839</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>9.223265898385581</v>
+        <v>21.07554648875478</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>6.297784761719347</v>
+        <v>1.099642602712516</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3057409359326946</v>
+        <v>0.0284555683819281</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1446</v>
+        <v>1418</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>373.3012756619653</v>
+        <v>444.8731500542925</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>13.45</v>
+        <v>18.35</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.79083546893993</v>
+        <v>54.51443357731458</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15.83515279347555</v>
+        <v>36.81030467384512</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7516506774851708</v>
+        <v>0.3088194597535635</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0093374397222259</v>
+        <v>0.0601583909338959</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1203</v>
+        <v>1417</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>371.8568866267639</v>
+        <v>440.476686773276</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>43.7</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>49.46102426807751</v>
+        <v>47.79093113917227</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>10.03210640395125</v>
+        <v>18.81700542541797</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.1517528566099533</v>
+        <v>0.8743941423928137</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0396019612262302</v>
+        <v>0.0186783072816868</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1459</v>
+        <v>1414</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>371.5798502633707</v>
+        <v>439.1018460300134</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>18.1</v>
+        <v>17.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>61.78926150403955</v>
+        <v>45.45205329693819</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>63.03496326611885</v>
+        <v>22.70429680856678</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5579850263370709</v>
+        <v>0.916617441390791</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1399136653339069</v>
+        <v>0.0977395505171756</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1216</v>
+        <v>1201</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>369.604330143224</v>
+        <v>435.2277580317904</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>76</v>
+        <v>11.6</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>56.61200229901108</v>
+        <v>42.66603945480794</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.42174995228792</v>
+        <v>44.6504916089754</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.036796978896781</v>
+        <v>0.3802866657352925</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2254051934149402</v>
+        <v>0.0016901634117137</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1526</v>
+        <v>1515</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>366.5606320712529</v>
+        <v>428.9539520728241</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>15.3</v>
+        <v>29.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>50.62380713505777</v>
+        <v>44.67279164203381</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.90484467667104</v>
+        <v>7.896105914736621</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.118519962050936</v>
+        <v>1.493842449877549</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1050200197406839</v>
+        <v>0.0027923754920941</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1419</v>
+        <v>1227</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>364.5234532123401</v>
+        <v>427.7997170135408</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>28</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.92356576821287</v>
+        <v>45.22820574787313</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>11.56130389166342</v>
+        <v>21.34811290810069</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6452856793427433</v>
+        <v>0.4852298057604941</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0167566720194841</v>
+        <v>4.839130811584713e-05</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1414</v>
+        <v>1108</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>364.1018460300133</v>
+        <v>425.6580354390837</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>17.5</v>
+        <v>11.15</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.45205291656092</v>
+        <v>40.00233012379947</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.70429646251434</v>
+        <v>45.05932570321875</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.916617441390791</v>
+        <v>0.7163120984773829</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0977395508261084</v>
+        <v>0.0383872067779389</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1531</v>
+        <v>1413</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>355.224865817651</v>
+        <v>421.6027758505961</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>11.85</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.60835549849367</v>
+        <v>54.46760605842199</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17.73031825501428</v>
+        <v>7.857677384993904</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.677402978779903</v>
+        <v>1.13582074328155</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.055865088839716</v>
+        <v>0.0171158680372241</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1443</v>
+        <v>1215</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>351.2383667060445</v>
+        <v>420.6007011844574</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>22.85</v>
+        <v>106.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45.36293408299783</v>
+        <v>48.99849341373484</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>8.304204903471941</v>
+        <v>13.75382110202879</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.381688500103628</v>
+        <v>1.021724103636274</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0028037637127217</v>
+        <v>0.1040460665150629</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1512</v>
+        <v>1474</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>344.3010873250047</v>
+        <v>407.1026161704506</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>6.28</v>
+        <v>9.91</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.48943767845715</v>
+        <v>42.65224314502648</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.93214487621115</v>
+        <v>18.49073770173817</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3509967936263382</v>
+        <v>0.5422431940059793</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0283561878233621</v>
+        <v>0.0013061340907453</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1338</v>
+        <v>1438</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>340.3791972967462</v>
+        <v>406.369611879428</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>14.85</v>
+        <v>21.95</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>50.13732748667466</v>
+        <v>52.21684744157656</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>36.87106566629402</v>
+        <v>8.925772138299363</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.9629719890498104</v>
+        <v>0.7379797631650213</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0359618050523778</v>
+        <v>0.058602761323636</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1535</v>
+        <v>1236</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>334.511397212623</v>
+        <v>403.4649006676746</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>45.85</v>
+        <v>25.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>52.56863724679597</v>
+        <v>54.33099145698276</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.68190725992431</v>
+        <v>19.30742603772513</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7457678596910154</v>
+        <v>0.5339450922550657</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0795301865808289</v>
+        <v>0.0089230375713613</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1417</v>
+        <v>1210</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>330.4766867732761</v>
+        <v>398.7098074262263</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.79093124923303</v>
+        <v>39.11962942937692</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.81700534611155</v>
+        <v>26.94372854635392</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8743941423928137</v>
+        <v>1.04509588057432</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0186783072720731</v>
+        <v>-0.0035072049794983</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1201</v>
+        <v>1445</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>325.2277580317904</v>
+        <v>393.6468319297861</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.6660393965315</v>
+        <v>45.80239316183786</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>44.65049157157522</v>
+        <v>21.68831634729692</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3802866657352925</v>
+        <v>0.671309860428899</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0016901634357489</v>
+        <v>0.0384327356457416</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1453</v>
+        <v>1436</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>323.0753124990465</v>
+        <v>393.5926679214803</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>10.95</v>
+        <v>36.35</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.7484342116112</v>
+        <v>46.80271062271144</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.35498549600885</v>
+        <v>14.43368994828771</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.404164120396271</v>
+        <v>0.5000991321723423</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0106084348712037</v>
+        <v>0.0790516704100937</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1227</v>
+        <v>1470</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>317.7997170135408</v>
+        <v>385.0687972623246</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>28</v>
+        <v>24.1</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.22820569427569</v>
+        <v>51.45079504568898</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.34811281046581</v>
+        <v>8.776718034293577</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4852298057604941</v>
+        <v>0.2310998855305943</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>4.839135618622814e-05</v>
+        <v>-0.0307734169777032</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1108</v>
+        <v>1432</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>315.6580354390837</v>
+        <v>381.0692272048934</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>11.15</v>
+        <v>15</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>40.00233012379947</v>
+        <v>48.42739884957553</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.05932569806654</v>
+        <v>11.88475639837482</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7163120984773829</v>
+        <v>1.969079064698632</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.038387206789956</v>
+        <v>0.0070746513135861</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1527</v>
+        <v>1309</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>314.5705709233964</v>
+        <v>378.8221355462224</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>32.45</v>
+        <v>14.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.15346274360098</v>
+        <v>55.63131078820543</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10.88924277553342</v>
+        <v>34.81026815336055</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3932125075504592</v>
+        <v>0.9390829491065809</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0026305762068081</v>
+        <v>0.0374020220596056</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1467</v>
+        <v>1439</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>313.8731021661127</v>
+        <v>376.3785504971904</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>8.15</v>
+        <v>27.85</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.31639505275749</v>
+        <v>50.95513904387949</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.37626588704126</v>
+        <v>20.53079507923812</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2098913834480692</v>
+        <v>1.309262803046625</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0363304866258284</v>
+        <v>-0.5836781317836885</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1506</v>
+        <v>1459</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>310.986421725221</v>
+        <v>371.5798502633707</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>39.89569094501558</v>
+        <v>61.78926156019134</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>23.47793645685062</v>
+        <v>63.03496335994019</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.804088495902071</v>
+        <v>0.5579850263370709</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0128223301391251</v>
+        <v>0.1399136652721163</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>310.6007011844563</v>
+        <v>366.8114150452658</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>106.5</v>
+        <v>24.1</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.99849359283251</v>
+        <v>44.01810859438558</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.75382090581978</v>
+        <v>22.99854884479882</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.021724103636274</v>
+        <v>0.2011607460688337</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.1040460656738379</v>
+        <v>-0.0174469052618512</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1340</v>
+        <v>1522</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>306.4676167294701</v>
+        <v>356.7278104057354</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>5.14</v>
+        <v>26.55</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.90296653229378</v>
+        <v>50.55441245832709</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11.4018065006727</v>
+        <v>17.34151852399201</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.304595541919922</v>
+        <v>0.5999876418114208</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0072240680254378</v>
+        <v>0.0976637045298185</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1444</v>
+        <v>1535</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>298.9727639005664</v>
+        <v>354.511397212623</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>6.97</v>
+        <v>45.85</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>49.85634939606942</v>
+        <v>52.56863703973024</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.74869128788434</v>
+        <v>13.6819072808812</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5765887613160101</v>
+        <v>0.7457678596910154</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0281018524443198</v>
+        <v>0.0795301865808289</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1474</v>
+        <v>1443</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>297.1026161704506</v>
+        <v>351.2383667060445</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>9.91</v>
+        <v>22.85</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.65224287693821</v>
+        <v>45.36293408879417</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.49073811678751</v>
+        <v>8.304204913927226</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5422431940059793</v>
+        <v>1.381688500103628</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0013061341989</v>
+        <v>-0.0028037637968409</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1447</v>
+        <v>1339</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>296.24254874205</v>
+        <v>350.9750071087282</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>6.57</v>
+        <v>42.45</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.76388512650265</v>
+        <v>44.61211515335828</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.46125338176445</v>
+        <v>26.95345819522369</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6862655095723772</v>
+        <v>0.4623308823924334</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0318219630604869</v>
+        <v>0.0307606314468681</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1464</v>
+        <v>1213</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>293.9498303915008</v>
+        <v>346.2204368512577</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>9.92</v>
+        <v>7.46</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>38.91113704946502</v>
+        <v>52.26901838723819</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.64467199397891</v>
+        <v>8.531928264707224</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7225214213641927</v>
+        <v>0.5718042659018471</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0065146253092881</v>
+        <v>0.023767440693698</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1539</v>
+        <v>1338</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>292.7360747329498</v>
+        <v>340.3791972967462</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>15.6</v>
+        <v>14.85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.72288171866142</v>
+        <v>50.13732739308419</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>29.67650646050368</v>
+        <v>36.87106565209106</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.384757117429765</v>
+        <v>0.9629719890498104</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0166952539802402</v>
+        <v>0.0359618050523778</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1438</v>
+        <v>1537</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>291.369611879428</v>
+        <v>338.7682762712718</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>21.95</v>
+        <v>115</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>52.21684762390962</v>
+        <v>44.65253099949515</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8.92577205807855</v>
+        <v>31.81987661677023</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7379797631650213</v>
+        <v>0.5425956632199205</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0586027612755673</v>
+        <v>0.23115650199425</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1413</v>
+        <v>1232</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>286.6027758505961</v>
+        <v>336.4201683208039</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>154</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>54.46760609011989</v>
+        <v>47.22566847692956</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>7.857677392250113</v>
+        <v>10.76524253464896</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.13582074328155</v>
+        <v>0.9156896083688374</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0171158680852943</v>
+        <v>-0.009125306746083301</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1233</v>
+        <v>1453</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>286.2969589678682</v>
+        <v>323.0753124990465</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>28.1</v>
+        <v>10.95</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.42005877255501</v>
+        <v>48.74843417822512</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.92527693777996</v>
+        <v>16.35498559066453</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8676865344582009</v>
+        <v>1.404164120396271</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0156175481927836</v>
+        <v>0.0106084348712037</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1436</v>
+        <v>1472</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>278.5926679214803</v>
+        <v>316.1996792263021</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>36.35</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.8027106088949</v>
+        <v>52.71466164411519</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.43368992818525</v>
+        <v>8.454687879013207</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5000991321723423</v>
+        <v>1.045524406912314</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0790516704581576</v>
+        <v>0.7064966595617808</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1432</v>
+        <v>1527</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>271.0692272048927</v>
+        <v>314.5705709233966</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>15</v>
+        <v>32.45</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.42739894551293</v>
+        <v>44.15346271999623</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.88475619975358</v>
+        <v>10.88924302649348</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.969079064698632</v>
+        <v>0.3932125075504592</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.00707465130157</v>
+        <v>-0.0026305763269802</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>265.7090140421741</v>
+        <v>313.8731021661127</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>19</v>
+        <v>8.15</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>25.32175495029618</v>
+        <v>48.31639504037714</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>44.80510445110658</v>
+        <v>15.37626598383129</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5974810326008739</v>
+        <v>0.2098913834480692</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0406951742902624</v>
+        <v>0.036330486621021</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1538</v>
+        <v>1506</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>263.9546759462577</v>
+        <v>310.986421725221</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>59.64563963797608</v>
+        <v>39.89569088815361</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.00432927455609</v>
+        <v>23.47793643154362</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.059549104037004</v>
+        <v>0.804088495902071</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.7258922245420879</v>
+        <v>0.0128223301511415</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1463</v>
+        <v>1340</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>260.6212294008489</v>
+        <v>306.4676167294701</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>17.6</v>
+        <v>5.14</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>52.5521717311012</v>
+        <v>44.90296662915539</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.07963391929007</v>
+        <v>11.40180654836056</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2693276023187294</v>
+        <v>1.304595541919922</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0164995800420354</v>
+        <v>-0.0072240680302446</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1568</v>
+        <v>1466</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>260.5967475756868</v>
+        <v>299.2787534739605</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>31.05</v>
+        <v>14.4</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.88262790080795</v>
+        <v>38.68914799391396</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>25.55304207371161</v>
+        <v>15.986966573527</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.511321845814262</v>
+        <v>0.8367600538962759</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.04243793316422</v>
+        <v>-0.0059966180873357</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1225</v>
+        <v>1444</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>256.8114150452658</v>
+        <v>298.9727639005664</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>24.1</v>
+        <v>6.97</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>44.01810858493582</v>
+        <v>49.85634938955626</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>22.99854880585692</v>
+        <v>20.74869131076749</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.2011607460688337</v>
+        <v>0.5765887613160101</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0174469051657114</v>
+        <v>0.0281018524563378</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1218</v>
+        <v>1447</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>254.0163767320521</v>
+        <v>296.24254874205</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>14.55</v>
+        <v>6.57</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>50.72032751708326</v>
+        <v>48.76388506166052</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>5.166415029751153</v>
+        <v>21.46125339157597</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8512379852166637</v>
+        <v>0.6862655095723772</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0307296399252892</v>
+        <v>0.0318219630749072</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1410</v>
+        <v>1464</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>253.9695253685292</v>
+        <v>293.9498303915012</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>23.75</v>
+        <v>9.92</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>37.27863861312131</v>
+        <v>38.91113681660249</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>6.780859478672658</v>
+        <v>23.6446720061281</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.482128838440118</v>
+        <v>0.7225214213641927</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0019928494278093</v>
+        <v>0.0065146252972713</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1522</v>
+        <v>1539</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>246.7278104057354</v>
+        <v>292.7360747329498</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>26.55</v>
+        <v>15.6</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.5544123485426</v>
+        <v>47.7228815916573</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.34151855466034</v>
+        <v>29.67650655571138</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5999876418114208</v>
+        <v>1.384757117429765</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.09766370480621631</v>
+        <v>0.0166952539321725</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1460</v>
+        <v>1217</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>243.7939002906727</v>
+        <v>289.768238381712</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>6.15</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.09089386401149</v>
+        <v>53.59525759852632</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>26.66730361991507</v>
+        <v>13.98502757873297</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9224628350363486</v>
+        <v>0.6172653359163132</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0015053139294494</v>
+        <v>-0.0004109762222505</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1437</v>
+        <v>1233</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>243.0965985178405</v>
+        <v>286.2969589678681</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>31.3</v>
+        <v>28.1</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.4323391840116</v>
+        <v>50.42005877255501</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.79632035921697</v>
+        <v>12.92527701340752</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3390338994192666</v>
+        <v>0.8676865344582009</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1599812418464674</v>
+        <v>0.0156175481687487</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1451</v>
+        <v>1316</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>241.4879221212665</v>
+        <v>284.0828689915118</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>17.05</v>
+        <v>10.45</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46.27002538056863</v>
+        <v>46.622961154926</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.7576017746695</v>
+        <v>17.21034052156024</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6729356989171458</v>
+        <v>0.6338822497324955</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0139195460034726</v>
+        <v>-0.0243551205514432</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1339</v>
+        <v>1517</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>240.9750071087282</v>
+        <v>276.9150010276061</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>42.45</v>
+        <v>10.45</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.61211517842734</v>
+        <v>45.13237936314165</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>26.95345820868058</v>
+        <v>21.99865055284615</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.4623308823924334</v>
+        <v>0.517856145825153</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0307606315309879</v>
+        <v>0.0357377418541566</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1109</v>
+        <v>1473</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>235.1334220415051</v>
+        <v>265.7090140421725</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>13.2</v>
+        <v>19</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>37.51777309042011</v>
+        <v>25.32175480464281</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>43.4465908429981</v>
+        <v>44.80510444824247</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4997551473866551</v>
+        <v>0.5974810326008739</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0029620116271011</v>
+        <v>-0.0406951743263154</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1525</v>
+        <v>1463</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>231.8389821283593</v>
+        <v>260.621229400849</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>63.6</v>
+        <v>17.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>50.85009822625384</v>
+        <v>52.55217169705643</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.92338828202764</v>
+        <v>17.07963394132317</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7377281506041171</v>
+        <v>0.2693276023187294</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.8143307483070596</v>
+        <v>0.0164995800179996</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1537</v>
+        <v>1568</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>228.7682762712718</v>
+        <v>260.5967475756869</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>115</v>
+        <v>31.05</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>44.65253029579209</v>
+        <v>52.88262791569937</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>31.81987714741748</v>
+        <v>25.55304209147818</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5425956632199205</v>
+        <v>0.511321845814262</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.2311565043977121</v>
+        <v>-0.0424379332122893</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1232</v>
+        <v>1109</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>226.4201683208039</v>
+        <v>255.1334220415052</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>154</v>
+        <v>13.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.22566847692956</v>
+        <v>37.5177730029089</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>10.76524253589926</v>
+        <v>43.44659079954892</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.9156896083688374</v>
+        <v>0.4997551473866551</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.009125306746083301</v>
+        <v>-0.0029620116511351</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1307</v>
+        <v>1218</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>226.1388010897658</v>
+        <v>254.0163767320521</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>30.95</v>
+        <v>14.55</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>49.62362506450486</v>
+        <v>50.72032754481101</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11.76338517761895</v>
+        <v>5.166415043547181</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7590752251399391</v>
+        <v>0.8512379852166637</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0580610124401879</v>
+        <v>0.0307296399012541</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1423</v>
+        <v>1410</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>226.1043378593239</v>
+        <v>253.9695253685292</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>34.75</v>
+        <v>23.75</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.1489746753719</v>
+        <v>37.27863859981711</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>7.934433717936892</v>
+        <v>6.780859526841337</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.613963302876389</v>
+        <v>0.482128838440118</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.2447898881055085</v>
+        <v>-0.0019928494278093</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1442</v>
+        <v>1423</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>216.388486891525</v>
+        <v>246.1043378593239</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>26.6</v>
+        <v>34.75</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>35.04601682389277</v>
+        <v>51.14897467333396</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>31.88795368984524</v>
+        <v>7.934433914169703</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.1933442758540263</v>
+        <v>0.613963302876389</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.2273493907979695</v>
+        <v>0.2447898881055085</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1532</v>
+        <v>1460</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>212.7603191982448</v>
+        <v>243.7939002906727</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>21.75</v>
+        <v>6.15</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>35.15927461270138</v>
+        <v>34.09089388321875</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>21.26698269329423</v>
+        <v>26.66730360086916</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.8506726480114899</v>
+        <v>0.9224628350363486</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.07065202335242721</v>
+        <v>-0.0015053139390632</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1457</v>
+        <v>1437</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>211.484068784505</v>
+        <v>243.0965985178405</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14.35</v>
+        <v>31.3</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.60801713768812</v>
+        <v>39.43233911645366</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.99520880081703</v>
+        <v>13.79632035921697</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.8638575015263227</v>
+        <v>0.3390338994192666</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0137345650080904</v>
+        <v>-0.1599812418464674</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1213</v>
+        <v>1451</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>206.2204368512577</v>
+        <v>241.4879221212666</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>7.46</v>
+        <v>17.05</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>52.26901623774281</v>
+        <v>46.27002547411166</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8.531927433806919</v>
+        <v>17.75760194228351</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5718042659018471</v>
+        <v>0.6729356989171458</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0237674437100412</v>
+        <v>0.013919545979438</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1472</v>
+        <v>1525</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>206.1996792263023</v>
+        <v>231.8389821283596</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>52.71466166671251</v>
+        <v>50.85009822488797</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>8.454687846030689</v>
+        <v>12.92338833787437</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.045524406912314</v>
+        <v>0.7377281506041171</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.7064966596098476</v>
+        <v>0.8143307482349498</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1536</v>
+        <v>1307</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>198.8913418399252</v>
+        <v>226.1388010897658</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>45.55</v>
+        <v>30.95</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.57209562946397</v>
+        <v>49.62362507705697</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>8.306478698239294</v>
+        <v>11.76338519048559</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.96407581839704</v>
+        <v>0.7590752251399391</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.047512917748655</v>
+        <v>0.0580610123560676</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1582</v>
+        <v>1442</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>197.8828852529539</v>
+        <v>216.3884868915205</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>71</v>
+        <v>26.6</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.80974622217644</v>
+        <v>35.04601687307304</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.9328550311799</v>
+        <v>31.88795370028956</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.899198262107239</v>
+        <v>0.1933442758540263</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1780636717378483</v>
+        <v>-0.2273493910142772</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1324</v>
+        <v>1532</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>196.4866325150767</v>
+        <v>212.7603191982449</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>9.99</v>
+        <v>21.75</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.16883298887809</v>
+        <v>35.1592744487893</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.91903070463659</v>
+        <v>21.26698276304739</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5601298259458414</v>
+        <v>0.8506726480114899</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0002458185539543</v>
+        <v>-0.0706520233764652</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1466</v>
+        <v>1457</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>189.2787534739606</v>
+        <v>211.4840687845049</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>14.4</v>
+        <v>14.35</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.68914817971396</v>
+        <v>49.60801697108698</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.98696645683092</v>
+        <v>16.99520889051936</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8367600538962759</v>
+        <v>0.8638575015263227</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0059966181474208</v>
+        <v>-0.0137345649960724</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1533</v>
+        <v>1536</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>181.2826100362526</v>
+        <v>198.8913418399252</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>29.9</v>
+        <v>45.55</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>37.61898281203916</v>
+        <v>35.57209565889416</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.04502314775567</v>
+        <v>8.306478767107354</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.302756199862827</v>
+        <v>1.96407581839704</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0332732454241098</v>
+        <v>0.0475129173400654</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1217</v>
+        <v>1582</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>179.7682383817116</v>
+        <v>197.8828852529539</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>71</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>53.59525759852632</v>
+        <v>45.80974617126918</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.98502755459521</v>
+        <v>17.93285500516888</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6172653359163132</v>
+        <v>0.899198262107239</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0004109762102336</v>
+        <v>0.178063671569601</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>174.0828689915118</v>
+        <v>196.4866325150763</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>10.45</v>
+        <v>9.99</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.62296106896634</v>
+        <v>49.1688324936495</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.21034047646656</v>
+        <v>16.91903070463659</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.6338822497324955</v>
+        <v>0.5601298259458414</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,11 +6771,11 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0243551205033738</v>
+        <v>-0.0002458185539543</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>172.0859583023691</v>
+        <v>192.085958302369</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>20.3</v>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>50.80835874933481</v>
+        <v>50.80835874156192</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.16203225093876</v>
+        <v>15.16203220943942</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>1.380689101031164</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.4158185094439248</v>
+        <v>0.415818509431909</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1517</v>
+        <v>1219</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>166.9150010276061</v>
+        <v>183.6728318180785</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>10.45</v>
+        <v>11.2</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45.13237936314165</v>
+        <v>42.26340773041624</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>21.99865048167262</v>
+        <v>13.1850387351985</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.517856145825153</v>
+        <v>0.756609018488461</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0357377418781921</v>
+        <v>-0.0242912027757002</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1110</v>
+        <v>1533</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>164.8694335874252</v>
+        <v>181.2826100362526</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>14.4</v>
+        <v>29.9</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>29.5137754792905</v>
+        <v>37.6189829866705</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>39.6237702471622</v>
+        <v>13.04502325497844</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.1999903418017603</v>
+        <v>1.302756199862827</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0330751296567939</v>
+        <v>0.033273245400077</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1465</v>
+        <v>1110</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>164.0506476421498</v>
+        <v>164.8694335874252</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>11.7</v>
+        <v>14.4</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.66740805347874</v>
+        <v>29.51377555307894</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>22.15823458943537</v>
+        <v>39.6237703828854</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.1645455334810834</v>
+        <v>0.1999903418017603</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0257872132282308</v>
+        <v>-0.0330751297168789</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1256</v>
+        <v>1465</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>152.4990250685561</v>
+        <v>164.0506476421498</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>168</v>
+        <v>11.7</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>41.51788078783709</v>
+        <v>46.66740821792289</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>7.389171848208025</v>
+        <v>22.15823458943537</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5442453165456669</v>
+        <v>0.1645455334810834</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.2803190269456213</v>
+        <v>0.0257872132162128</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1540</v>
+        <v>1256</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>138.7034895839285</v>
+        <v>152.4990250685561</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>18.85</v>
+        <v>168</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>35.79105684847119</v>
+        <v>41.5178807306343</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>10.69864685396012</v>
+        <v>7.389171838602308</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.362741621496443</v>
+        <v>0.5442453165456669</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0395694932630432</v>
+        <v>0.2803190271859885</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1231</v>
+        <v>1540</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>138.612711874414</v>
+        <v>138.7034895839285</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>77.5</v>
+        <v>18.85</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>29.40053530791968</v>
+        <v>35.79105686583637</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>18.40684909752623</v>
+        <v>10.69864686837487</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.291676924479292</v>
+        <v>1.362741621496443</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1206113849356197</v>
+        <v>-0.0395694934312831</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1471</v>
+        <v>1231</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>138.6058215608046</v>
+        <v>138.6127118744146</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>40.83447194582646</v>
+        <v>29.40053530791968</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>11.32330611007494</v>
+        <v>18.40684928044104</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2.204054511353528</v>
+        <v>1.291676924479292</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0007890099174232</v>
+        <v>-0.1206113851759651</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1529</v>
+        <v>1471</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>132.9790194266393</v>
+        <v>138.6058215608046</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>15.45</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>41.83368874747601</v>
+        <v>40.83447176415903</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18.83788543375543</v>
+        <v>11.3233060799299</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5546359247429877</v>
+        <v>2.204054511353528</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.06634051135518849</v>
+        <v>-0.0007890099174232</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1468</v>
+        <v>1529</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>125.2219034659431</v>
+        <v>132.9790194266394</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>13.15</v>
+        <v>15.45</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>48.13185909089825</v>
+        <v>41.83368869759198</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>8.868648998334892</v>
+        <v>18.8378854162468</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.9528727027579116</v>
+        <v>0.5546359247429877</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-7.454540806256862e-05</v>
+        <v>0.0663405112229986</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1435</v>
+        <v>1468</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>123.2248321787139</v>
+        <v>125.2219034659431</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0</v>
+        <v>13.15</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>24.92835240921248</v>
+        <v>48.13185898970829</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>9.260643803155851</v>
+        <v>8.868649037990046</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.0500644393774164</v>
+        <v>0.9528727027579116</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-1.327194641520324</v>
+        <v>-7.454545613166594e-05</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1475</v>
+        <v>1435</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>77.54014915348313</v>
+        <v>123.2248321787139</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>25.85</v>
+        <v>0</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>45.54936100124777</v>
+        <v>24.92835238944224</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>19.30650168978837</v>
+        <v>9.260644206985001</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.7664386591956193</v>
+        <v>0.0500644393774164</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0136684964222956</v>
+        <v>-1.327194642941763</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1219</v>
+        <v>1475</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>73.67283181807858</v>
+        <v>77.5401491534831</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>11.2</v>
+        <v>25.85</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>42.26340773041624</v>
+        <v>45.54936079868116</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>13.1850387150838</v>
+        <v>19.30650179748816</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.756609018488461</v>
+        <v>0.7664386591956193</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.0242912027516647</v>
+        <v>-0.0136684962780861</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>45.95434206769493</v>
+        <v>45.95434237764721</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>16.13272822778073</v>
+        <v>16.13272822948193</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.9260301920287216</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.0153497999277679</v>
+        <v>0.0153497999037335</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
